--- a/relatorio_nfp.xlsx
+++ b/relatorio_nfp.xlsx
@@ -471,7 +471,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45997</v>
+        <v>45999</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -500,7 +500,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45997</v>
+        <v>45999</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
